--- a/data/Data_Register.xlsx
+++ b/data/Data_Register.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>ho</t>
   </si>
@@ -41,6 +41,9 @@
     <t>matkhau</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
     <t>expected</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
     <t>Thomhihi</t>
   </si>
   <si>
+    <t>register_success</t>
+  </si>
+  <si>
     <t>TÀI KHOẢN CỦA BẠN</t>
   </si>
   <si>
@@ -71,6 +77,9 @@
     <t>hfdt*g</t>
   </si>
   <si>
+    <t>email_invalid</t>
+  </si>
+  <si>
     <t>please include an '@' in the email address. 'thomhihi2004' is missing an '@'.</t>
   </si>
   <si>
@@ -80,7 +89,16 @@
     <t>Thom@04</t>
   </si>
   <si>
+    <t>ho_empty</t>
+  </si>
+  <si>
     <t>Please fill out this field.</t>
+  </si>
+  <si>
+    <t>email_empty</t>
+  </si>
+  <si>
+    <t>password_empty</t>
   </si>
 </sst>
 </file>
@@ -93,7 +111,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,17 +120,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -440,12 +468,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -566,148 +609,154 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -722,7 +771,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1242,110 +1291,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.2857142857143" customWidth="1"/>
     <col min="2" max="2" width="13.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="24.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="28.8571428571429" customWidth="1"/>
     <col min="4" max="4" width="15.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="72.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="19.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="74.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" ht="16.5" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" ht="16.5" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="E2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" ht="16.5" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" ht="16.5" spans="1:6">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" ht="16.5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:6">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
